--- a/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>ATXS</t>
   </si>
@@ -656,92 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -793,8 +796,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -846,8 +852,11 @@
       <c r="S9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -899,8 +908,11 @@
       <c r="S10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,61 +932,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E12" s="3">
         <v>13300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>9100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>8000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>10400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>167200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>7800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,8 +1042,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1079,8 +1098,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1132,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,61 +1175,65 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E17" s="3">
         <v>20200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>170100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>8000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,52 +1241,55 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-15100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-13500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-14300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-9500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-170100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-8000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,8 +1309,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1289,23 +1322,23 @@
         <v>2500</v>
       </c>
       <c r="F20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G20" s="3">
         <v>2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1325,13 +1358,16 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1368,23 +1404,26 @@
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P21" s="3">
         <v>-9000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-8000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1430,67 +1469,73 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-17700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-11200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-15300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-9500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-170100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-8000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1542,8 +1587,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-11200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-170100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-8000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-11200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-170100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1807,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,8 +1979,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1925,23 +1994,23 @@
         <v>-2500</v>
       </c>
       <c r="F32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1961,66 +2030,72 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-11200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-170100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-11200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-170100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,91 +2310,95 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E41" s="3">
         <v>119800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>134000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>202300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>46000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>29800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>86500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>131800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>139500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>146900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>69000</v>
+        <v>71000</v>
       </c>
       <c r="E42" s="3">
         <v>69000</v>
       </c>
       <c r="F42" s="3">
+        <v>69000</v>
+      </c>
+      <c r="G42" s="3">
         <v>11000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>205900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>70600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>72700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>66100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>39000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2317,22 +2406,25 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>20000</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q42" s="3">
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R42" s="3">
         <v>2000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>41800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2384,8 +2476,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2437,114 +2532,123 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E45" s="3">
         <v>2700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>250900</v>
+      </c>
+      <c r="E46" s="3">
         <v>191500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>204400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>215400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>227700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>118500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>103800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>114200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>127100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>134500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>140100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>147700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>46300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>55500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>55600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>57100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2596,61 +2700,67 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2702,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,16 +2924,19 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2000</v>
       </c>
       <c r="F52" s="3">
         <v>2000</v>
@@ -2826,7 +2945,7 @@
         <v>2000</v>
       </c>
       <c r="H52" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="I52" s="3">
         <v>200</v>
@@ -2835,13 +2954,13 @@
         <v>200</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
@@ -2859,10 +2978,13 @@
         <v>200</v>
       </c>
       <c r="S52" s="3">
+        <v>200</v>
+      </c>
+      <c r="T52" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>254700</v>
+      </c>
+      <c r="E54" s="3">
         <v>193900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>207100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>218200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>230600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>119800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>105300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>114700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>127500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>135100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>140900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>148700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>47500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>56900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>57100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>59200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,61 +3138,65 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>800</v>
       </c>
       <c r="H57" s="3">
         <v>800</v>
       </c>
       <c r="I57" s="3">
+        <v>800</v>
+      </c>
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
-      </c>
-      <c r="L57" s="3">
-        <v>600</v>
       </c>
       <c r="M57" s="3">
         <v>600</v>
       </c>
       <c r="N57" s="3">
+        <v>600</v>
+      </c>
+      <c r="O57" s="3">
         <v>1800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3115,114 +3248,123 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E60" s="3">
         <v>9400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3274,8 +3416,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3283,52 +3428,55 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>600</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3">
         <v>100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E66" s="3">
         <v>9400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3681,7 +3848,7 @@
         <v>95300</v>
       </c>
       <c r="G70" s="3">
-        <v>96400</v>
+        <v>95300</v>
       </c>
       <c r="H70" s="3">
         <v>96400</v>
@@ -3699,14 +3866,14 @@
         <v>96400</v>
       </c>
       <c r="M70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="N70" s="3">
         <v>99800</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>240900</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-580500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-549100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-531400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-518800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-507600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-494400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-482400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-471100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-455800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-446300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-438400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-431000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-260900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-251900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-241100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-231500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-223600</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E76" s="3">
         <v>89200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>105100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>116000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>124800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-101100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>50900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>53700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-31400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-11200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-170100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,8 +4419,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4269,14 +4467,17 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-14300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-10700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-13300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-12600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4632,11 +4852,11 @@
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -4658,8 +4878,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
@@ -4667,8 +4887,11 @@
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-57900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>195000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-135200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-27100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-39000</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>26400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-20000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>39700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4900,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,29 +5301,32 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>88000</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>120400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24300</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
         <v>0</v>
       </c>
@@ -5095,25 +5340,28 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>104300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>8900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>6300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>25600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5165,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-68300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>181800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-25400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-39700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-45300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-7700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>122000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>38500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>ATXS</t>
   </si>
@@ -656,95 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,8 +803,11 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -855,8 +862,11 @@
       <c r="T9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -911,8 +921,11 @@
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,64 +946,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E12" s="3">
         <v>26900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>13300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>9100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>8000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>167200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>7800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1101,8 +1121,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,64 +1202,68 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E17" s="3">
         <v>34200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>20200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>170100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>8000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1241,55 +1271,58 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-34200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-20200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-11400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-9500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-170100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-8000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,8 +1343,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1319,29 +1353,29 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="F20" s="3">
         <v>2500</v>
       </c>
       <c r="G20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H20" s="3">
         <v>2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1361,21 +1395,24 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
+      <c r="E21" s="3">
+        <v>-31400</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>4</v>
@@ -1407,23 +1444,26 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-10900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-9500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-8000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1472,70 +1512,76 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-31400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-17700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-12600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-11200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-13300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-15300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-170100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-8000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1590,8 +1636,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-17700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-12600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-13300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-170100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-8000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-31400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-12600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-13300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-170100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,8 +2049,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1991,29 +2061,29 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>-2500</v>
+        <v>-2800</v>
       </c>
       <c r="F32" s="3">
         <v>-2500</v>
       </c>
       <c r="G32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2033,69 +2103,75 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-31400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-12600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-13300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-170100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-31400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-12600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-13300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-170100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,97 +2397,101 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>172000</v>
+      </c>
+      <c r="E41" s="3">
         <v>175500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>119800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>134000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>202300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>46000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>29800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>86500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>131800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>139500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>146900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>52900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>51900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>197900</v>
+      </c>
+      <c r="E42" s="3">
         <v>71000</v>
-      </c>
-      <c r="E42" s="3">
-        <v>69000</v>
       </c>
       <c r="F42" s="3">
         <v>69000</v>
       </c>
       <c r="G42" s="3">
+        <v>69000</v>
+      </c>
+      <c r="H42" s="3">
         <v>11000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>205900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>70600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>72700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>66100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>39000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -2409,22 +2499,25 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>20000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R42" s="3">
+      <c r="R42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S42" s="3">
         <v>2000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>41800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2479,8 +2572,11 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2535,120 +2631,129 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E45" s="3">
         <v>4400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>374500</v>
+      </c>
+      <c r="E46" s="3">
         <v>250900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>191500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>204400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>215400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>227700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>118500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>103800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>114200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>127100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>134500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>140100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>147700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>46300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>55500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>55600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>57100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2703,64 +2808,70 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,19 +3044,22 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E52" s="3">
         <v>3400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2000</v>
       </c>
       <c r="G52" s="3">
         <v>2000</v>
@@ -2948,7 +3068,7 @@
         <v>2000</v>
       </c>
       <c r="I52" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="J52" s="3">
         <v>200</v>
@@ -2957,13 +3077,13 @@
         <v>200</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
@@ -2981,10 +3101,13 @@
         <v>200</v>
       </c>
       <c r="T52" s="3">
+        <v>200</v>
+      </c>
+      <c r="U52" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>378800</v>
+      </c>
+      <c r="E54" s="3">
         <v>254700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>193900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>207100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>218200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>230600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>119800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>105300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>114700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>127500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>135100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>140900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>148700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>47500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>56900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>57100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>59200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,64 +3269,68 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>800</v>
       </c>
       <c r="I57" s="3">
         <v>800</v>
       </c>
       <c r="J57" s="3">
+        <v>800</v>
+      </c>
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
-      </c>
-      <c r="M57" s="3">
-        <v>600</v>
       </c>
       <c r="N57" s="3">
         <v>600</v>
       </c>
       <c r="O57" s="3">
+        <v>600</v>
+      </c>
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3251,120 +3385,129 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E59" s="3">
         <v>10000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E60" s="3">
         <v>11600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3419,64 +3562,70 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>600</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
       <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3">
         <v>100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3851,7 +4019,7 @@
         <v>95300</v>
       </c>
       <c r="H70" s="3">
-        <v>96400</v>
+        <v>95300</v>
       </c>
       <c r="I70" s="3">
         <v>96400</v>
@@ -3869,14 +4037,14 @@
         <v>96400</v>
       </c>
       <c r="N70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="O70" s="3">
         <v>99800</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>240900</v>
       </c>
-      <c r="P70" s="3">
-        <v>0</v>
-      </c>
       <c r="Q70" s="3">
         <v>0</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-600500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-580500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-549100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-531400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-518800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-507600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-494400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-482400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-471100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-455800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-446300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-438400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-431000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-260900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-251900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-241100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-231500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-223600</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>272400</v>
+      </c>
+      <c r="E76" s="3">
         <v>147800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>89200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>105100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>116000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>124800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>34000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-101100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>40700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>50900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>53700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-31400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-12600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-13300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-170100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,8 +4618,9 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4470,14 +4669,17 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-14300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-10700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-13300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-12600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,8 +5054,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4881,8 +5102,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
@@ -4890,8 +5111,11 @@
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-126200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-57900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>195000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-135200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-27100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39000</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>26400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>39700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,32 +5547,35 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>141800</v>
+      </c>
+      <c r="E100" s="3">
         <v>88000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>120400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>24300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -5343,25 +5589,28 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>104300</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>8900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>6300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>25600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E102" s="3">
         <v>55700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-68300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>181800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-25400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-45300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-7700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>122000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-28000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>38500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>ATXS</t>
   </si>
@@ -656,99 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -806,8 +810,11 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -865,8 +872,11 @@
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -924,8 +934,11 @@
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,67 +960,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E12" s="3">
         <v>15700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>26900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>13300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>9100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>8000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>7700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>10400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>167200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>7800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1082,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1124,8 +1144,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1206,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,67 +1229,71 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E17" s="3">
         <v>24200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>20200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>14300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>12400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>170100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>10900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1271,58 +1301,61 @@
         <v>4</v>
       </c>
       <c r="E18" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-34200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-20200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-15100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-12400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-15400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-9500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-10900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-8000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1377,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1353,32 +1387,32 @@
         <v>4</v>
       </c>
       <c r="E20" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F20" s="3">
         <v>2800</v>
-      </c>
-      <c r="F20" s="3">
-        <v>2500</v>
       </c>
       <c r="G20" s="3">
         <v>2500</v>
       </c>
       <c r="H20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1398,13 +1432,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1412,11 +1449,11 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-31400</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1447,23 +1484,26 @@
       <c r="P21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3">
         <v>-9000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-10900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-9500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1515,73 +1555,79 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-19900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-31400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-17700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-11200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-8000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1639,8 +1685,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-19900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-12600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-8000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-19900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-31400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-12600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2119,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2061,32 +2131,32 @@
         <v>4</v>
       </c>
       <c r="E32" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2800</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-2500</v>
       </c>
       <c r="G32" s="3">
         <v>-2500</v>
       </c>
       <c r="H32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2106,72 +2176,78 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-19900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-12600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-19900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-12600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,103 +2484,107 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87200</v>
+      </c>
+      <c r="E41" s="3">
         <v>172000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>175500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>119800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>134000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>202300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>46000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>29800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>86500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>131800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>139500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>146900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>52900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>51900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>267500</v>
+      </c>
+      <c r="E42" s="3">
         <v>197900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>71000</v>
-      </c>
-      <c r="F42" s="3">
-        <v>69000</v>
       </c>
       <c r="G42" s="3">
         <v>69000</v>
       </c>
       <c r="H42" s="3">
+        <v>69000</v>
+      </c>
+      <c r="I42" s="3">
         <v>11000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>205900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>70600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>72700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>66100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>39000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2502,22 +2592,25 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>20000</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="S42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T42" s="3">
         <v>2000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>41800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2575,8 +2668,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2634,126 +2730,135 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E45" s="3">
         <v>4600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>357900</v>
+      </c>
+      <c r="E46" s="3">
         <v>374500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>250900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>191500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>204400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>215400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>227700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>118500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>103800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>114200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>127100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>134500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>140100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>147700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>46300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>55500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>55600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>57100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2811,67 +2916,73 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,22 +3164,25 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
         <v>4100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2000</v>
       </c>
       <c r="H52" s="3">
         <v>2000</v>
@@ -3071,7 +3191,7 @@
         <v>2000</v>
       </c>
       <c r="J52" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="K52" s="3">
         <v>200</v>
@@ -3080,13 +3200,13 @@
         <v>200</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
@@ -3104,10 +3224,13 @@
         <v>200</v>
       </c>
       <c r="U52" s="3">
+        <v>200</v>
+      </c>
+      <c r="V52" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>368000</v>
+      </c>
+      <c r="E54" s="3">
         <v>378800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>254700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>193900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>207100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>218200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>230600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>119800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>105300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>114700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>127500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>135100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>140900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>148700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>47500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>56900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>59200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,67 +3400,71 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
-      </c>
-      <c r="I57" s="3">
-        <v>800</v>
       </c>
       <c r="J57" s="3">
         <v>800</v>
       </c>
       <c r="K57" s="3">
+        <v>800</v>
+      </c>
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
-      </c>
-      <c r="N57" s="3">
-        <v>600</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
       <c r="P57" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3388,126 +3522,135 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E59" s="3">
         <v>10200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E60" s="3">
         <v>11100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>6400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3565,67 +3708,73 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="D62" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
       <c r="G62" s="3">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3">
         <v>100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
       <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
         <v>100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20900</v>
+      </c>
+      <c r="E66" s="3">
         <v>11100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4022,7 +4190,7 @@
         <v>95300</v>
       </c>
       <c r="I70" s="3">
-        <v>96400</v>
+        <v>95300</v>
       </c>
       <c r="J70" s="3">
         <v>96400</v>
@@ -4040,14 +4208,14 @@
         <v>96400</v>
       </c>
       <c r="O70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="P70" s="3">
         <v>99800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>240900</v>
       </c>
-      <c r="Q70" s="3">
-        <v>0</v>
-      </c>
       <c r="R70" s="3">
         <v>0</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-624600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-600500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-580500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-549100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-531400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-518800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-507600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-494400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-482400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-471100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-455800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-446300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-438400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-431000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-260900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-251900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-241100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-231500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-223600</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>251800</v>
+      </c>
+      <c r="E76" s="3">
         <v>272400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>147800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>89200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>105100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>116000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>124800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>34000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-101100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>40700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>50900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>53700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-19900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-12600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-170100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4672,14 +4871,17 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-19100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-14300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-10700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-13300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-12600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,13 +5275,14 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -5076,11 +5297,11 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -5105,8 +5326,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -5114,8 +5335,11 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-68100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-126200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-57900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>195000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-135200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-27100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39000</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>26400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-20000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>39700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,35 +5793,38 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>141800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>88000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>300</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>120400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -5592,25 +5838,28 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>104300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>8900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>6300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>25600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-84800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>55700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-14200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-68300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>181800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-25400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-45300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>122000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-28000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>38500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>ATXS</t>
   </si>
@@ -656,126 +656,130 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -813,8 +817,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -875,8 +882,11 @@
       <c r="V9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -937,8 +947,11 @@
       <c r="V10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -961,70 +974,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E12" s="3">
         <v>20700</v>
       </c>
-      <c r="E12" s="3">
-        <v>15700</v>
-      </c>
       <c r="F12" s="3">
-        <v>26900</v>
+        <v>15600</v>
       </c>
       <c r="G12" s="3">
+        <v>11300</v>
+      </c>
+      <c r="H12" s="3">
         <v>13300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>9100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>8000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>7700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>167200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>7800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,31 +1102,34 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>15200</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1147,8 +1167,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1209,8 +1232,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1256,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29000</v>
+      </c>
+      <c r="E17" s="3">
         <v>28800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>24200</v>
       </c>
-      <c r="F17" s="3">
-        <v>34200</v>
-      </c>
       <c r="G17" s="3">
+        <v>19000</v>
+      </c>
+      <c r="H17" s="3">
         <v>20200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>12400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>170100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>8000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>4</v>
+      <c r="D18" s="3">
+        <v>-29000</v>
       </c>
       <c r="E18" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-24200</v>
       </c>
-      <c r="F18" s="3">
-        <v>-34200</v>
-      </c>
       <c r="G18" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-20200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-15100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-12400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-9500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-170100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-8000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,44 +1411,45 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1435,36 +1469,39 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>4</v>
+      <c r="D21" s="3">
+        <v>-29100</v>
       </c>
       <c r="E21" s="3">
-        <v>-19900</v>
+        <v>-28800</v>
       </c>
       <c r="F21" s="3">
-        <v>-31400</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>4</v>
+        <v>-24200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-13500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>4</v>
@@ -1487,46 +1524,49 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3">
         <v>-9000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-10900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1558,99 +1598,105 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-19900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-31400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-17700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-15300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-170100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-8000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1688,8 +1734,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1799,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-19900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-17700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-170100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-19900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-31400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-17700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-170100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1994,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2059,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2124,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,44 +2189,47 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-4200</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-2800</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-2500</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>-2300</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2179,75 +2249,81 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-19900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-31400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-17700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-170100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2384,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-19900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-31400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-17700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-170100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2546,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,109 +2571,113 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80900</v>
+      </c>
+      <c r="E41" s="3">
         <v>87200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>172000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>175500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>119800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>134000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>202300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>46000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>29800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>86500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>131800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>139500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>146900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>52900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>51900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>13300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>263400</v>
+      </c>
+      <c r="E42" s="3">
         <v>267500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>197900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>71000</v>
-      </c>
-      <c r="G42" s="3">
-        <v>69000</v>
       </c>
       <c r="H42" s="3">
         <v>69000</v>
       </c>
       <c r="I42" s="3">
+        <v>69000</v>
+      </c>
+      <c r="J42" s="3">
         <v>11000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>205900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>70600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>72700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>66100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>39000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -2595,45 +2685,48 @@
         <v>0</v>
       </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>20000</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T42" s="3">
+      <c r="T42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U42" s="3">
         <v>2000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>41800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2671,31 +2764,34 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2733,155 +2829,164 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4400</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="H45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
+        <v>500</v>
+      </c>
+      <c r="R45" s="3">
+        <v>800</v>
+      </c>
+      <c r="S45" s="3">
         <v>1400</v>
       </c>
-      <c r="N45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="T45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
-        <v>500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>800</v>
-      </c>
-      <c r="R45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W45" s="3">
         <v>2700</v>
       </c>
-      <c r="T45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="U45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="V45" s="3">
-        <v>2700</v>
-      </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>351900</v>
+      </c>
+      <c r="E46" s="3">
         <v>357900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>374500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>250900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>191500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>204400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>215400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>227700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>118500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>103800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>114200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>127100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>134500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>140100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>147700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>46300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>55500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>55600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>57100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2919,70 +3024,76 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3043,8 +3154,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3219,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,8 +3284,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3176,16 +3296,16 @@
         <v>4400</v>
       </c>
       <c r="E52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F52" s="3">
         <v>4100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2000</v>
       </c>
       <c r="I52" s="3">
         <v>2000</v>
@@ -3194,7 +3314,7 @@
         <v>2000</v>
       </c>
       <c r="K52" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="L52" s="3">
         <v>200</v>
@@ -3203,13 +3323,13 @@
         <v>200</v>
       </c>
       <c r="N52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
@@ -3227,10 +3347,13 @@
         <v>200</v>
       </c>
       <c r="V52" s="3">
+        <v>200</v>
+      </c>
+      <c r="W52" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3414,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>361600</v>
+      </c>
+      <c r="E54" s="3">
         <v>368000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>378800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>254700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>193900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>207100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>218200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>230600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>119800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>105300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>127500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>135100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>140900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>148700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>47500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>56900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>57100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>59200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3506,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,93 +3531,97 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
-      </c>
-      <c r="J57" s="3">
-        <v>800</v>
       </c>
       <c r="K57" s="3">
         <v>800</v>
       </c>
       <c r="L57" s="3">
+        <v>800</v>
+      </c>
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
-      </c>
-      <c r="O57" s="3">
-        <v>600</v>
       </c>
       <c r="P57" s="3">
         <v>600</v>
       </c>
       <c r="Q57" s="3">
+        <v>600</v>
+      </c>
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3525,140 +3659,149 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>14000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>10200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>8200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>5800</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K59" s="3">
+        <v>8300</v>
+      </c>
+      <c r="L59" s="3">
         <v>5700</v>
       </c>
-      <c r="J59" s="3">
-        <v>8300</v>
-      </c>
-      <c r="K59" s="3">
-        <v>5700</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E60" s="3">
         <v>16400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -3670,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3711,70 +3854,76 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>4500</v>
+      <c r="D62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
+        <v>500</v>
+      </c>
+      <c r="M62" s="3">
+        <v>600</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
         <v>100</v>
       </c>
-      <c r="I62" s="3">
-        <v>200</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="R62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="S62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
-        <v>500</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>4600</v>
-      </c>
-      <c r="R62" s="3">
-        <v>400</v>
-      </c>
-      <c r="S62" s="3">
-        <v>600</v>
-      </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3984,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4049,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4114,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E66" s="3">
         <v>20900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4206,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4269,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4334,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4193,7 +4361,7 @@
         <v>95300</v>
       </c>
       <c r="J70" s="3">
-        <v>96400</v>
+        <v>95300</v>
       </c>
       <c r="K70" s="3">
         <v>96400</v>
@@ -4211,14 +4379,14 @@
         <v>96400</v>
       </c>
       <c r="P70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="Q70" s="3">
         <v>99800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>240900</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4231,8 +4399,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4464,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-649200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-624600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-600500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-580500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-549100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-531400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-518800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-507600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-494400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-482400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-471100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-455800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-446300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-438400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-431000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-260900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-251900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-241100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-231500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-223600</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4594,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4659,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4724,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>246300</v>
+      </c>
+      <c r="E76" s="3">
         <v>251800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>272400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>147800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>89200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>105100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>116000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>124800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>34000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>37100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-101100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>40700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>50900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>53700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4854,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-19900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-31400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-17700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-170100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,31 +5016,32 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4874,14 +5073,17 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5144,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5209,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5274,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5339,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5404,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-16800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-19100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-14300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-10700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-13300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-12600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-7500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,19 +5496,20 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -5300,11 +5521,11 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -5329,8 +5550,8 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>4</v>
@@ -5338,8 +5559,11 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5624,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5689,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-68100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-126200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-57900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>195000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-135200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-27100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-39000</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
         <v>0</v>
       </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>26400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-20000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>2000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>39700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,31 +5781,32 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5610,8 +5844,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5909,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5974,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,38 +6039,41 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>141800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>88000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>300</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>120400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>24300</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -5841,48 +6087,51 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>104300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>8900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>6300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>25600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5920,66 +6169,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-84800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>55700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-14200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-68300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>181800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-45300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-7700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>122000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-28000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>ATXS</t>
   </si>
@@ -656,107 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -781,8 +784,8 @@
       <c r="J8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -820,8 +823,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -885,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -950,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -975,73 +987,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E12" s="3">
         <v>20500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>15600</v>
       </c>
-      <c r="G12" s="3">
-        <v>11300</v>
-      </c>
       <c r="H12" s="3">
+        <v>11600</v>
+      </c>
+      <c r="I12" s="3">
         <v>13300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>9100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>8000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>7700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>167200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>7800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1105,8 +1121,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1119,20 +1138,20 @@
       <c r="F14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3">
         <v>15200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1170,8 +1189,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1235,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1257,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E17" s="3">
         <v>29000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>28800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>24200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>20200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>170100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-28800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-24200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-20200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-11400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-9500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-170100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-9000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-8000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1412,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1439,20 +1472,20 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1472,40 +1505,43 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-29100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-28800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-24200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-19000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-20300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1527,23 +1563,26 @@
       <c r="R21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T21" s="3">
         <v>-9000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-10900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1568,8 +1607,8 @@
       <c r="J22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1601,79 +1640,85 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-19900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-31400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-17700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-11200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-15300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-170100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-8000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1698,8 +1743,8 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1737,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1802,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-19900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-17700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-11200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-170100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-8000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-19900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-11200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-170100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1997,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2062,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2127,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2192,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2219,20 +2288,20 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2252,78 +2321,84 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-19900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-17700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-170100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2387,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-19900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-17700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-170100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2547,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2572,115 +2657,119 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E41" s="3">
         <v>80900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>87200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>172000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>175500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>119800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>134000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>202300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>46000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>29800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>86500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>131800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>139500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>146900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>52900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>51900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>13300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>268300</v>
+      </c>
+      <c r="E42" s="3">
         <v>263400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>267500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>197900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>71000</v>
-      </c>
-      <c r="H42" s="3">
-        <v>69000</v>
       </c>
       <c r="I42" s="3">
         <v>69000</v>
       </c>
       <c r="J42" s="3">
+        <v>69000</v>
+      </c>
+      <c r="K42" s="3">
         <v>11000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>205900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>70600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>72700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>66100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -2688,22 +2777,25 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>20000</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V42" s="3">
         <v>2000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>41800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2728,8 +2820,8 @@
       <c r="J43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2767,8 +2859,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2793,8 +2888,8 @@
       <c r="J44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2832,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2858,112 +2956,118 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>334600</v>
+      </c>
+      <c r="E46" s="3">
         <v>351900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>357900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>374500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>250900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>191500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>204400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>215400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>227700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>118500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>103800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>114200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>127100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>134500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>140100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>147700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>46300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>55500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>55600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>57100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2988,8 +3092,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3027,73 +3131,79 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3157,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3222,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3287,28 +3403,31 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4400</v>
+        <v>2600</v>
       </c>
       <c r="E52" s="3">
         <v>4400</v>
       </c>
       <c r="F52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="G52" s="3">
         <v>4100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2000</v>
       </c>
       <c r="J52" s="3">
         <v>2000</v>
@@ -3317,7 +3436,7 @@
         <v>2000</v>
       </c>
       <c r="L52" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="M52" s="3">
         <v>200</v>
@@ -3326,13 +3445,13 @@
         <v>200</v>
       </c>
       <c r="O52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>200</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
@@ -3350,10 +3469,13 @@
         <v>200</v>
       </c>
       <c r="W52" s="3">
+        <v>200</v>
+      </c>
+      <c r="X52" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3417,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>342400</v>
+      </c>
+      <c r="E54" s="3">
         <v>361600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>368000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>378800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>254700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>193900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>207100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>218200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>230600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>119800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>105300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>114700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>127500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>135100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>140900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>148700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>47500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>56900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>57100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>59200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3507,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3532,73 +3661,77 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
-      </c>
-      <c r="K57" s="3">
-        <v>800</v>
       </c>
       <c r="L57" s="3">
         <v>800</v>
       </c>
       <c r="M57" s="3">
+        <v>800</v>
+      </c>
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
-      </c>
-      <c r="P57" s="3">
-        <v>600</v>
       </c>
       <c r="Q57" s="3">
         <v>600</v>
       </c>
       <c r="R57" s="3">
+        <v>600</v>
+      </c>
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3606,25 +3739,25 @@
         <v>1400</v>
       </c>
       <c r="E58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
-      </c>
-      <c r="I58" s="3">
-        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>600</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3662,8 +3795,11 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3688,124 +3824,130 @@
       <c r="J59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
         <v>8300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E60" s="3">
         <v>15700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4500</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
         <v>0</v>
       </c>
@@ -3813,14 +3955,14 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -3857,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3883,47 +4028,50 @@
       <c r="J62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>600</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3987,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4052,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4117,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E66" s="3">
         <v>20000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4207,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4272,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4337,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4364,7 +4531,7 @@
         <v>95300</v>
       </c>
       <c r="K70" s="3">
-        <v>96400</v>
+        <v>95300</v>
       </c>
       <c r="L70" s="3">
         <v>96400</v>
@@ -4382,14 +4549,14 @@
         <v>96400</v>
       </c>
       <c r="Q70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="R70" s="3">
         <v>99800</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>240900</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4402,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4467,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-674800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-649200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-624600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-600500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-580500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-549100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-531400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-518800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-507600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-494400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-482400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-471100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-455800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-446300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-438400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-431000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-260900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-251900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-241100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-231500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-223600</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4597,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4662,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4727,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>223900</v>
+      </c>
+      <c r="E76" s="3">
         <v>246300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>251800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>272400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>147800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>89200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>105100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>116000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>124800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>25900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>37100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-101100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>40700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>50900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4857,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-19900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-17700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-170100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5017,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5043,8 +5241,8 @@
       <c r="J83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5076,14 +5274,17 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5147,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5212,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5277,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5342,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5407,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-16800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-19100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-14300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-10700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-12600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-6300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-7500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5497,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5506,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -5524,11 +5744,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -5553,8 +5773,8 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
@@ -5562,8 +5782,11 @@
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5627,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5692,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E94" s="3">
         <v>6200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-68100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-126200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
         <v>-57900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>195000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-135200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-27100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-39000</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>26400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-20000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>2000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>39700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5782,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5808,8 +6041,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5847,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5912,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5977,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6042,41 +6284,44 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>15300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>141800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>88000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>120400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>24300</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
@@ -6090,25 +6335,28 @@
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>104300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>8900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>25600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6133,8 +6381,8 @@
       <c r="J101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6172,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-84800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>55700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-68300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>181800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-39700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-45300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>122000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-28000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>38500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
   <si>
     <t>ATXS</t>
   </si>
@@ -656,110 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -787,8 +791,8 @@
       <c r="K8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -826,8 +830,11 @@
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -894,8 +901,11 @@
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +972,11 @@
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,76 +1001,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E12" s="3">
         <v>19900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>20500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>15600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>11600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>13300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>9100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>8000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>9600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>7700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>10400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>167200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>7800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>6800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1141,20 +1161,20 @@
       <c r="G14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
         <v>15200</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E17" s="3">
         <v>29600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>28800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>24200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>20200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>14300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>170100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>9600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-28800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-24200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-20200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-11400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-170100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,13 +1478,14 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1475,20 +1509,20 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1508,43 +1542,46 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-29600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-29100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-24200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-19000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-20300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13500</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1566,23 +1603,26 @@
       <c r="S21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3">
         <v>-9000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-10900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-9500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1610,8 +1650,8 @@
       <c r="K22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1643,82 +1683,88 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-24500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-31400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-15300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-170100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-8000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1746,8 +1792,8 @@
       <c r="K24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-19900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-17700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-170100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-8000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-19900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-31900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-170100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,13 +2328,16 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2291,20 +2361,20 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2324,81 +2394,87 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="X32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-19900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-17700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-31900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-170100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-19900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-17700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-31900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-170100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,121 +2744,125 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E41" s="3">
         <v>59800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>80900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>87200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>172000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>175500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>119800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>134000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>202300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>46000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>29800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>86500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>131800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>139500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>146900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>52900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>240700</v>
+      </c>
+      <c r="E42" s="3">
         <v>268300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>263400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>267500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>197900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>71000</v>
-      </c>
-      <c r="I42" s="3">
-        <v>69000</v>
       </c>
       <c r="J42" s="3">
         <v>69000</v>
       </c>
       <c r="K42" s="3">
+        <v>69000</v>
+      </c>
+      <c r="L42" s="3">
         <v>11000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>205900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>70600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>72700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>66100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -2780,22 +2870,25 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>20000</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W42" s="3">
         <v>2000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>41800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2823,8 +2916,8 @@
       <c r="K43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2862,8 +2955,11 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2891,8 +2987,8 @@
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2930,8 +3026,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2959,115 +3058,121 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>303000</v>
+      </c>
+      <c r="E46" s="3">
         <v>334600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>351900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>357900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>374500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>250900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>191500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>204400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>215400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>227700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>118500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>103800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>114200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>127100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>134500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>140100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>147700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>46300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>55500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>55600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>57100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3095,8 +3200,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3134,76 +3239,82 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E48" s="3">
         <v>5100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3523,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3415,22 +3535,22 @@
         <v>2600</v>
       </c>
       <c r="E52" s="3">
-        <v>4400</v>
+        <v>2600</v>
       </c>
       <c r="F52" s="3">
         <v>4400</v>
       </c>
       <c r="G52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H52" s="3">
         <v>4100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2000</v>
       </c>
       <c r="K52" s="3">
         <v>2000</v>
@@ -3439,7 +3559,7 @@
         <v>2000</v>
       </c>
       <c r="M52" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
@@ -3448,13 +3568,13 @@
         <v>200</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
-      </c>
-      <c r="R52" s="3">
-        <v>200</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
@@ -3472,10 +3592,13 @@
         <v>200</v>
       </c>
       <c r="X52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y52" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>310400</v>
+      </c>
+      <c r="E54" s="3">
         <v>342400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>361600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>368000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>378800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>254700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>193900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>207100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>218200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>230600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>119800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>105300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>114700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>127500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>135100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>140900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>148700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>47500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>56900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>57100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,76 +3792,80 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>800</v>
       </c>
       <c r="M57" s="3">
         <v>800</v>
       </c>
       <c r="N57" s="3">
+        <v>800</v>
+      </c>
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>600</v>
       </c>
       <c r="R57" s="3">
         <v>600</v>
       </c>
       <c r="S57" s="3">
+        <v>600</v>
+      </c>
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3742,25 +3876,25 @@
         <v>1400</v>
       </c>
       <c r="F58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G58" s="3">
         <v>1200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>600</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3798,8 +3932,11 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3827,130 +3964,136 @@
       <c r="K59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M59" s="3">
         <v>8300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E60" s="3">
         <v>19100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E61" s="3">
         <v>4000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4500</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
         <v>0</v>
       </c>
@@ -3958,14 +4101,14 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4031,47 +4177,50 @@
       <c r="K62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>600</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E66" s="3">
         <v>23100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>20000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4534,7 +4702,7 @@
         <v>95300</v>
       </c>
       <c r="L70" s="3">
-        <v>96400</v>
+        <v>95300</v>
       </c>
       <c r="M70" s="3">
         <v>96400</v>
@@ -4552,14 +4720,14 @@
         <v>96400</v>
       </c>
       <c r="R70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="S70" s="3">
         <v>99800</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>240900</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-708500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-674800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-649200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-624600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-600500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-580500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-549100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-531400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-518800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-507600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-494400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-482400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-471100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-455800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-446300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-438400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-431000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-260900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-251900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-241100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-231500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-223600</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E76" s="3">
         <v>223900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>246300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>251800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>272400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>147800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>89200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>105100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>116000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>124800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>25900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>34000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>37100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-101100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>40700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>50900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>53700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-19900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-17700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-31900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-170100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5244,8 +5443,8 @@
       <c r="K83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -5277,14 +5476,17 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-17400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-28000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-16800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-19100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-14300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-12600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-6300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-7500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,25 +5937,26 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -5747,11 +5968,11 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -5776,8 +5997,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -5785,8 +6006,11 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>6200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-126200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-57900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>195000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-135200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-27100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>26400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-20000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>2000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>39700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6044,8 +6278,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,44 +6530,47 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>15300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>141800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>88000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>120400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>24300</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -6338,25 +6584,28 @@
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>104300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>8900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>25600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6384,8 +6633,8 @@
       <c r="K101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-84800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>55700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-14200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-68300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>181800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-39700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-7700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>122000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-28000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ATXS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>ATXS</t>
   </si>
@@ -656,114 +656,118 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -794,8 +798,8 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -833,8 +837,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -904,8 +911,11 @@
       <c r="Y9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -975,8 +985,11 @@
       <c r="Y10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,79 +1015,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E12" s="3">
         <v>27600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>19900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>20500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>20700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>15600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>13300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>9100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>8000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>9600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>7700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>10400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>167200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>7800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1161,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1164,20 +1184,20 @@
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="3">
         <v>15200</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1215,8 +1235,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1286,8 +1309,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E17" s="3">
         <v>37000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>28800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>24200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>19000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>14300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>12400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>170100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-29600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-24200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-20200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-170100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-6700</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1512,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1488,7 +1522,7 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1512,20 +1546,20 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1545,46 +1579,49 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-37100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-29600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-29100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-24200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-19000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-20300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>4</v>
       </c>
@@ -1606,23 +1643,26 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3">
         <v>-9000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-10900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-9500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1653,8 +1693,8 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1686,85 +1726,91 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-33700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-24500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-24200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-31400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-17700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-170100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1795,8 +1841,8 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1834,8 +1880,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-33700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-19900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-17700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-170100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-10900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-33700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-19900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-170100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-10900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2398,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2340,7 +2410,7 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2364,20 +2434,20 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2397,84 +2467,90 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-33700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-19900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-17700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-170100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-10900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-33700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-19900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-17700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-170100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-10900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,127 +2831,131 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>76300</v>
+      </c>
+      <c r="E41" s="3">
         <v>54400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>59800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>80900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>172000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>175500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>119800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>134000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>202300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>29800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>86500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>131800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>139500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>146900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>24900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>52900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E42" s="3">
         <v>240700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>268300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>263400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>267500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>197900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>71000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>69000</v>
       </c>
       <c r="K42" s="3">
         <v>69000</v>
       </c>
       <c r="L42" s="3">
+        <v>69000</v>
+      </c>
+      <c r="M42" s="3">
         <v>11000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>205900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>70600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>66100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>39000</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -2873,22 +2963,25 @@
         <v>0</v>
       </c>
       <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
         <v>20000</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X42" s="3">
         <v>2000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>41800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>26300</v>
       </c>
     </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2919,8 +3012,8 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -2958,8 +3051,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2990,8 +3086,8 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3029,8 +3125,11 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3061,118 +3160,124 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>268600</v>
+      </c>
+      <c r="E46" s="3">
         <v>303000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>334600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>351900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>357900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>374500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>250900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>191500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>204400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>215400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>227700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>118500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>103800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>114200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>127100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>134500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>140100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>147700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>46300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>55500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>55600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>57100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>39000</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3203,8 +3308,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3242,79 +3347,85 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3384,8 +3495,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,34 +3643,37 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2600</v>
+        <v>8800</v>
       </c>
       <c r="E52" s="3">
         <v>2600</v>
       </c>
       <c r="F52" s="3">
-        <v>4400</v>
+        <v>2600</v>
       </c>
       <c r="G52" s="3">
         <v>4400</v>
       </c>
       <c r="H52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I52" s="3">
         <v>4100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>2000</v>
       </c>
       <c r="L52" s="3">
         <v>2000</v>
@@ -3562,7 +3682,7 @@
         <v>2000</v>
       </c>
       <c r="N52" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
@@ -3571,13 +3691,13 @@
         <v>200</v>
       </c>
       <c r="Q52" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
-      </c>
-      <c r="S52" s="3">
-        <v>200</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
@@ -3595,10 +3715,13 @@
         <v>200</v>
       </c>
       <c r="Y52" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z52" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>281900</v>
+      </c>
+      <c r="E54" s="3">
         <v>310400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>342400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>361600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>368000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>378800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>254700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>193900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>207100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>218200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>230600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>119800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>105300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>114700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>127500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>135100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>140900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>148700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>47500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>56900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>57100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>59200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>41800</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +3923,83 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>800</v>
       </c>
       <c r="N57" s="3">
         <v>800</v>
       </c>
       <c r="O57" s="3">
+        <v>800</v>
+      </c>
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
-      </c>
-      <c r="R57" s="3">
-        <v>600</v>
       </c>
       <c r="S57" s="3">
         <v>600</v>
       </c>
       <c r="T57" s="3">
+        <v>600</v>
+      </c>
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3879,25 +4013,25 @@
         <v>1400</v>
       </c>
       <c r="G58" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H58" s="3">
         <v>1200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
-      </c>
-      <c r="K58" s="3">
-        <v>600</v>
       </c>
       <c r="L58" s="3">
         <v>600</v>
       </c>
       <c r="M58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3935,8 +4069,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3967,136 +4104,142 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N59" s="3">
         <v>8300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>6400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>5500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4500</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -4104,14 +4247,14 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4148,8 +4291,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4180,47 +4326,50 @@
       <c r="L62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E66" s="3">
         <v>21100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>20000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>20900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4705,7 +4873,7 @@
         <v>95300</v>
       </c>
       <c r="M70" s="3">
-        <v>96400</v>
+        <v>95300</v>
       </c>
       <c r="N70" s="3">
         <v>96400</v>
@@ -4723,14 +4891,14 @@
         <v>96400</v>
       </c>
       <c r="S70" s="3">
+        <v>96400</v>
+      </c>
+      <c r="T70" s="3">
         <v>99800</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>240900</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-741600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-708500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-674800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-649200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-624600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-600500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-580500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-549100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-531400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-518800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-507600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-494400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-482400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-471100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-455800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-446300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-438400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-431000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-260900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-251900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-241100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-231500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-223600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>165200</v>
+      </c>
+      <c r="E76" s="3">
         <v>194000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>223900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>246300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>251800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>272400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>147800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>89200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>105100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>116000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>124800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>25900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>34000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>37100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-101100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>40700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>49300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>50900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>53700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-33700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-19900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-17700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-170100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-10900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6600</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5446,8 +5645,8 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -5479,14 +5678,17 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-34000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-17400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-16800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-19100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-14300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-7500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-7800</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,28 +6158,29 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -5971,11 +6192,11 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -6000,8 +6221,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
@@ -6009,8 +6230,11 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E94" s="3">
         <v>28600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>6200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-68100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-126200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-57900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>195000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-135200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-27100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-39000</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>26400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-20000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>2000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>39700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6281,8 +6515,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,47 +6776,50 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>15300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>141800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>88000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>120400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>24300</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
         <v>0</v>
       </c>
@@ -6587,25 +6833,28 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>104300</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>8900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>25600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6636,8 +6885,8 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-84800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-3500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>55700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-14200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-68300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>181800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-39700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-45300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>122000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-28000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-7500</v>
       </c>
     </row>
